--- a/PCB V3/SLSS LightRail/SLSS LightRail BoM.xlsx
+++ b/PCB V3/SLSS LightRail/SLSS LightRail BoM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\PCB V3\SLSS LightRail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{75B85B58-8936-48FE-87A8-9B2C26D995EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C547107-A28E-48EB-9C83-8B2FB02ADA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{880E9649-882B-4599-9FFC-07E01271A5D7}"/>
   </bookViews>
@@ -1008,6 +1008,10 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="3" max="3" width="11.453125" customWidth="1"/>
+    <col min="4" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="38.81640625" customWidth="1"/>
+    <col min="8" max="8" width="30.81640625" customWidth="1"/>
     <col min="9" max="9" width="18.453125" customWidth="1"/>
     <col min="10" max="10" width="23.81640625" customWidth="1"/>
     <col min="11" max="11" width="15.36328125" customWidth="1"/>

--- a/PCB V3/SLSS LightRail/SLSS LightRail BoM.xlsx
+++ b/PCB V3/SLSS LightRail/SLSS LightRail BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\PCB V3\SLSS LightRail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/PCB V3/SLSS LightRail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C547107-A28E-48EB-9C83-8B2FB02ADA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7C547107-A28E-48EB-9C83-8B2FB02ADA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C68451-01DF-48ED-8B04-105C089F30A9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{880E9649-882B-4599-9FFC-07E01271A5D7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{880E9649-882B-4599-9FFC-07E01271A5D7}"/>
   </bookViews>
   <sheets>
     <sheet name="SLSS LightRail" sheetId="1" r:id="rId1"/>
